--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575070468</v>
+        <v>46157.9311922363</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9311922363</v>
+        <v>46157.93184656016</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93184656016</v>
+        <v>46157.93406463985</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406463985</v>
+        <v>46157.93724499906</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724499906</v>
+        <v>46158.28222187367</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222187367</v>
+        <v>46158.29704614102</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29704614102</v>
+        <v>46158.29822076092</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822076092</v>
+        <v>46158.33393146028</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393146028</v>
+        <v>46158.36862933268</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Шакалов- слесарь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862933268</v>
+        <v>46158.37293899939</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
